--- a/exports/INOXWIND_full_report.xlsx
+++ b/exports/INOXWIND_full_report.xlsx
@@ -18,9 +18,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
+  <numFmts count="4">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
+    <numFmt numFmtId="166" formatCode="yyyy-mm-dd"/>
+    <numFmt numFmtId="167" formatCode="YYYY-MM-DD"/>
   </numFmts>
   <fonts count="1">
     <font>
@@ -51,10 +53,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -420,7 +423,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q65"/>
+  <dimension ref="A1:U65"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -509,6 +512,26 @@
           <t>candles_held</t>
         </is>
       </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>expiry</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>reached_expiry</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>rule_trades</t>
+        </is>
+      </c>
+      <c r="U1" t="inlineStr">
+        <is>
+          <t>rule_wins</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -534,28 +557,28 @@
         <v>9.56</v>
       </c>
       <c r="G2" s="1" t="n">
-        <v>44582.55208333334</v>
+        <v>44585.38541666666</v>
       </c>
       <c r="H2" t="n">
-        <v>31.44</v>
+        <v>29.18</v>
       </c>
       <c r="I2" t="n">
         <v>29.69573923607937</v>
       </c>
       <c r="J2" s="2" t="n">
-        <v>11.16666666666667</v>
+        <v>14</v>
       </c>
       <c r="K2" t="n">
-        <v>1.75</v>
+        <v>-5.57</v>
       </c>
       <c r="L2" t="n">
-        <v>5.4</v>
+        <v>6.38</v>
       </c>
       <c r="M2" t="n">
-        <v>0.32</v>
+        <v>2.04</v>
       </c>
       <c r="N2" t="n">
-        <v>5.03</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="O2" t="n">
         <v>8.460000000000001</v>
@@ -564,7 +587,19 @@
         <v>1</v>
       </c>
       <c r="Q2" t="n">
-        <v>20</v>
+        <v>21</v>
+      </c>
+      <c r="R2" s="3" t="n">
+        <v>44588</v>
+      </c>
+      <c r="S2" t="b">
+        <v>0</v>
+      </c>
+      <c r="T2" t="n">
+        <v>1</v>
+      </c>
+      <c r="U2" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="3">
@@ -591,28 +626,28 @@
         <v>16.42</v>
       </c>
       <c r="G3" s="1" t="n">
-        <v>44596.55208333334</v>
+        <v>44599.38541666666</v>
       </c>
       <c r="H3" t="n">
-        <v>31.79</v>
+        <v>32.78</v>
       </c>
       <c r="I3" t="n">
         <v>32.34126609689814</v>
       </c>
       <c r="J3" s="2" t="n">
-        <v>11.16666666666667</v>
+        <v>14</v>
       </c>
       <c r="K3" t="n">
-        <v>-8.94</v>
+        <v>-12.34</v>
       </c>
       <c r="L3" t="n">
-        <v>10.11</v>
+        <v>14.02</v>
       </c>
       <c r="M3" t="n">
         <v>3.98</v>
       </c>
       <c r="N3" t="n">
-        <v>3.81</v>
+        <v>6.67</v>
       </c>
       <c r="O3" t="n">
         <v>-8.300000000000001</v>
@@ -621,7 +656,19 @@
         <v>1</v>
       </c>
       <c r="Q3" t="n">
-        <v>18</v>
+        <v>19</v>
+      </c>
+      <c r="R3" s="3" t="n">
+        <v>44588</v>
+      </c>
+      <c r="S3" t="b">
+        <v>1</v>
+      </c>
+      <c r="T3" t="n">
+        <v>2</v>
+      </c>
+      <c r="U3" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="4">
@@ -648,28 +695,28 @@
         <v>9.529999999999999</v>
       </c>
       <c r="G4" s="1" t="n">
-        <v>44603.55208333334</v>
+        <v>44606.38541666666</v>
       </c>
       <c r="H4" t="n">
-        <v>31.44</v>
+        <v>29.72</v>
       </c>
       <c r="I4" t="n">
         <v>30.11821148048056</v>
       </c>
       <c r="J4" s="2" t="n">
-        <v>4.166666666666667</v>
+        <v>7</v>
       </c>
       <c r="K4" t="n">
-        <v>-4.09</v>
+        <v>-9.33</v>
       </c>
       <c r="L4" t="n">
-        <v>4.82</v>
+        <v>11.13</v>
       </c>
       <c r="M4" t="n">
         <v>1.78</v>
       </c>
       <c r="N4" t="n">
-        <v>5.37</v>
+        <v>5.95</v>
       </c>
       <c r="O4" t="n">
         <v>6.67</v>
@@ -678,7 +725,19 @@
         <v>1</v>
       </c>
       <c r="Q4" t="n">
-        <v>10</v>
+        <v>11</v>
+      </c>
+      <c r="R4" s="3" t="n">
+        <v>44616</v>
+      </c>
+      <c r="S4" t="b">
+        <v>0</v>
+      </c>
+      <c r="T4" t="n">
+        <v>1</v>
+      </c>
+      <c r="U4" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="5">
@@ -705,19 +764,19 @@
         <v>13.43</v>
       </c>
       <c r="G5" s="1" t="n">
-        <v>44663.38541666666</v>
+        <v>44663.55208333334</v>
       </c>
       <c r="H5" t="n">
-        <v>26.61</v>
+        <v>29.08</v>
       </c>
       <c r="I5" t="n">
         <v>28.38941011892305</v>
       </c>
       <c r="J5" s="2" t="n">
-        <v>57</v>
+        <v>57.16666666666666</v>
       </c>
       <c r="K5" t="n">
-        <v>10.46</v>
+        <v>2.15</v>
       </c>
       <c r="L5" t="n">
         <v>6.46</v>
@@ -735,7 +794,19 @@
         <v>1</v>
       </c>
       <c r="Q5" t="n">
-        <v>79</v>
+        <v>80</v>
+      </c>
+      <c r="R5" s="3" t="n">
+        <v>44616</v>
+      </c>
+      <c r="S5" t="b">
+        <v>1</v>
+      </c>
+      <c r="T5" t="n">
+        <v>3</v>
+      </c>
+      <c r="U5" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="6">
@@ -762,19 +833,19 @@
         <v>13.51</v>
       </c>
       <c r="G6" s="1" t="n">
-        <v>44676.55208333334</v>
+        <v>44677.38541666666</v>
       </c>
       <c r="H6" t="n">
-        <v>27.5</v>
+        <v>27.21</v>
       </c>
       <c r="I6" t="n">
         <v>27.248777390887</v>
       </c>
       <c r="J6" s="2" t="n">
-        <v>13</v>
+        <v>13.83333333333333</v>
       </c>
       <c r="K6" t="n">
-        <v>-5.43</v>
+        <v>-6.43</v>
       </c>
       <c r="L6" t="n">
         <v>8.630000000000001</v>
@@ -792,7 +863,19 @@
         <v>1</v>
       </c>
       <c r="Q6" t="n">
-        <v>15</v>
+        <v>16</v>
+      </c>
+      <c r="R6" s="3" t="n">
+        <v>44679</v>
+      </c>
+      <c r="S6" t="b">
+        <v>0</v>
+      </c>
+      <c r="T6" t="n">
+        <v>1</v>
+      </c>
+      <c r="U6" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="7">
@@ -819,19 +902,19 @@
         <v>13.87</v>
       </c>
       <c r="G7" s="1" t="n">
-        <v>44714.55208333334</v>
+        <v>44715.38541666666</v>
       </c>
       <c r="H7" t="n">
-        <v>23.16</v>
+        <v>23.56</v>
       </c>
       <c r="I7" t="n">
         <v>23.55042263477026</v>
       </c>
       <c r="J7" s="2" t="n">
-        <v>37.16666666666666</v>
+        <v>38</v>
       </c>
       <c r="K7" t="n">
-        <v>14.88</v>
+        <v>13.41</v>
       </c>
       <c r="L7" t="n">
         <v>4.15</v>
@@ -849,7 +932,19 @@
         <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>54</v>
+        <v>55</v>
+      </c>
+      <c r="R7" s="3" t="n">
+        <v>44679</v>
+      </c>
+      <c r="S7" t="b">
+        <v>1</v>
+      </c>
+      <c r="T7" t="n">
+        <v>3</v>
+      </c>
+      <c r="U7" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="8">
@@ -876,22 +971,22 @@
         <v>9.09</v>
       </c>
       <c r="G8" s="1" t="n">
-        <v>44727.55208333334</v>
+        <v>44728.38541666666</v>
       </c>
       <c r="H8" t="n">
-        <v>21.88</v>
+        <v>20.8</v>
       </c>
       <c r="I8" t="n">
         <v>21.4173549047896</v>
       </c>
       <c r="J8" s="2" t="n">
-        <v>12.16666666666667</v>
+        <v>13</v>
       </c>
       <c r="K8" t="n">
-        <v>-7.13</v>
+        <v>-11.71</v>
       </c>
       <c r="L8" t="n">
-        <v>10.27</v>
+        <v>11.71</v>
       </c>
       <c r="M8" t="n">
         <v>2.23</v>
@@ -906,7 +1001,19 @@
         <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>18</v>
+        <v>19</v>
+      </c>
+      <c r="R8" s="3" t="n">
+        <v>44742</v>
+      </c>
+      <c r="S8" t="b">
+        <v>0</v>
+      </c>
+      <c r="T8" t="n">
+        <v>1</v>
+      </c>
+      <c r="U8" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="9">
@@ -933,19 +1040,19 @@
         <v>13.73</v>
       </c>
       <c r="G9" s="1" t="n">
-        <v>44768.38541666666</v>
+        <v>44768.55208333334</v>
       </c>
       <c r="H9" t="n">
-        <v>20.65</v>
+        <v>21.49</v>
       </c>
       <c r="I9" t="n">
         <v>20.72904998928384</v>
       </c>
       <c r="J9" s="2" t="n">
-        <v>40</v>
+        <v>40.16666666666666</v>
       </c>
       <c r="K9" t="n">
-        <v>0.72</v>
+        <v>-3.32</v>
       </c>
       <c r="L9" t="n">
         <v>6.39</v>
@@ -963,7 +1070,19 @@
         <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>57</v>
+        <v>58</v>
+      </c>
+      <c r="R9" s="3" t="n">
+        <v>44742</v>
+      </c>
+      <c r="S9" t="b">
+        <v>1</v>
+      </c>
+      <c r="T9" t="n">
+        <v>2</v>
+      </c>
+      <c r="U9" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="10">
@@ -990,19 +1109,19 @@
         <v>10.59</v>
       </c>
       <c r="G10" s="1" t="n">
-        <v>44823.38541666666</v>
+        <v>44823.55208333334</v>
       </c>
       <c r="H10" t="n">
-        <v>36.67</v>
+        <v>34.7</v>
       </c>
       <c r="I10" t="n">
         <v>34.79187919711158</v>
       </c>
       <c r="J10" s="2" t="n">
-        <v>54.83333333333334</v>
+        <v>55</v>
       </c>
       <c r="K10" t="n">
-        <v>70.64</v>
+        <v>61.47</v>
       </c>
       <c r="L10" t="n">
         <v>5.07</v>
@@ -1020,7 +1139,19 @@
         <v>1</v>
       </c>
       <c r="Q10" t="n">
-        <v>72</v>
+        <v>73</v>
+      </c>
+      <c r="R10" s="3" t="n">
+        <v>44770</v>
+      </c>
+      <c r="S10" t="b">
+        <v>1</v>
+      </c>
+      <c r="T10" t="n">
+        <v>3</v>
+      </c>
+      <c r="U10" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="11">
@@ -1047,22 +1178,22 @@
         <v>16.74</v>
       </c>
       <c r="G11" s="1" t="n">
-        <v>44841.55208333334</v>
+        <v>44844.38541666666</v>
       </c>
       <c r="H11" t="n">
-        <v>37.51</v>
+        <v>38.44</v>
       </c>
       <c r="I11" t="n">
         <v>38.29858180966669</v>
       </c>
       <c r="J11" s="2" t="n">
-        <v>18</v>
+        <v>20.83333333333333</v>
       </c>
       <c r="K11" t="n">
-        <v>-8.1</v>
+        <v>-10.78</v>
       </c>
       <c r="L11" t="n">
-        <v>8.5</v>
+        <v>12.07</v>
       </c>
       <c r="M11" t="n">
         <v>2.62</v>
@@ -1077,7 +1208,19 @@
         <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>27</v>
+        <v>28</v>
+      </c>
+      <c r="R11" s="3" t="n">
+        <v>44833</v>
+      </c>
+      <c r="S11" t="b">
+        <v>1</v>
+      </c>
+      <c r="T11" t="n">
+        <v>2</v>
+      </c>
+      <c r="U11" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="12">
@@ -1104,19 +1247,19 @@
         <v>11.86</v>
       </c>
       <c r="G12" s="1" t="n">
-        <v>44874.55208333334</v>
+        <v>44875.38541666666</v>
       </c>
       <c r="H12" t="n">
-        <v>35.39</v>
+        <v>34.94</v>
       </c>
       <c r="I12" t="n">
         <v>34.95679199458772</v>
       </c>
       <c r="J12" s="2" t="n">
-        <v>30.16666666666667</v>
+        <v>31</v>
       </c>
       <c r="K12" t="n">
-        <v>-7.93</v>
+        <v>-9.109999999999999</v>
       </c>
       <c r="L12" t="n">
         <v>10.25</v>
@@ -1134,7 +1277,19 @@
         <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>41</v>
+        <v>42</v>
+      </c>
+      <c r="R12" s="3" t="n">
+        <v>44861</v>
+      </c>
+      <c r="S12" t="b">
+        <v>1</v>
+      </c>
+      <c r="T12" t="n">
+        <v>2</v>
+      </c>
+      <c r="U12" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="13">
@@ -1161,19 +1316,19 @@
         <v>10.17</v>
       </c>
       <c r="G13" s="1" t="n">
-        <v>44979.55208333334</v>
+        <v>44980.38541666666</v>
       </c>
       <c r="H13" t="n">
-        <v>24.05</v>
+        <v>25.14</v>
       </c>
       <c r="I13" t="n">
         <v>24.78815580799832</v>
       </c>
       <c r="J13" s="2" t="n">
-        <v>104.1666666666667</v>
+        <v>105</v>
       </c>
       <c r="K13" t="n">
-        <v>31.17</v>
+        <v>28.05</v>
       </c>
       <c r="L13" t="n">
         <v>2.4</v>
@@ -1191,7 +1346,19 @@
         <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>146</v>
+        <v>147</v>
+      </c>
+      <c r="R13" s="3" t="n">
+        <v>44889</v>
+      </c>
+      <c r="S13" t="b">
+        <v>1</v>
+      </c>
+      <c r="T13" t="n">
+        <v>4</v>
+      </c>
+      <c r="U13" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="14">
@@ -1218,19 +1385,19 @@
         <v>11.41</v>
       </c>
       <c r="G14" s="1" t="n">
-        <v>44998.55208333334</v>
+        <v>44999.38541666666</v>
       </c>
       <c r="H14" t="n">
-        <v>26.61</v>
+        <v>25.68</v>
       </c>
       <c r="I14" t="n">
         <v>25.83462895778668</v>
       </c>
       <c r="J14" s="2" t="n">
-        <v>18.16666666666667</v>
+        <v>19</v>
       </c>
       <c r="K14" t="n">
-        <v>5.85</v>
+        <v>2.15</v>
       </c>
       <c r="L14" t="n">
         <v>6.09</v>
@@ -1248,7 +1415,19 @@
         <v>1</v>
       </c>
       <c r="Q14" t="n">
-        <v>24</v>
+        <v>25</v>
+      </c>
+      <c r="R14" s="3" t="n">
+        <v>45014</v>
+      </c>
+      <c r="S14" t="b">
+        <v>0</v>
+      </c>
+      <c r="T14" t="n">
+        <v>1</v>
+      </c>
+      <c r="U14" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="15">
@@ -1275,19 +1454,19 @@
         <v>12.62</v>
       </c>
       <c r="G15" s="1" t="n">
-        <v>45037.55208333334</v>
+        <v>45040.38541666666</v>
       </c>
       <c r="H15" t="n">
-        <v>24.54</v>
+        <v>25.48</v>
       </c>
       <c r="I15" t="n">
         <v>25.10135018966098</v>
       </c>
       <c r="J15" s="2" t="n">
-        <v>38.16666666666666</v>
+        <v>41</v>
       </c>
       <c r="K15" t="n">
-        <v>4.44</v>
+        <v>0.78</v>
       </c>
       <c r="L15" t="n">
         <v>4.01</v>
@@ -1296,7 +1475,7 @@
         <v>1.73</v>
       </c>
       <c r="N15" t="n">
-        <v>5.25</v>
+        <v>7.46</v>
       </c>
       <c r="O15" t="n">
         <v>-2.74</v>
@@ -1305,7 +1484,19 @@
         <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>50</v>
+        <v>51</v>
+      </c>
+      <c r="R15" s="3" t="n">
+        <v>45014</v>
+      </c>
+      <c r="S15" t="b">
+        <v>1</v>
+      </c>
+      <c r="T15" t="n">
+        <v>2</v>
+      </c>
+      <c r="U15" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="16">
@@ -1332,19 +1523,19 @@
         <v>10.71</v>
       </c>
       <c r="G16" s="1" t="n">
-        <v>45152.38541666666</v>
+        <v>45152.55208333334</v>
       </c>
       <c r="H16" t="n">
-        <v>50.57</v>
+        <v>49.04</v>
       </c>
       <c r="I16" t="n">
         <v>49.53512092977009</v>
       </c>
       <c r="J16" s="2" t="n">
-        <v>112</v>
+        <v>112.1666666666667</v>
       </c>
       <c r="K16" t="n">
-        <v>98.47</v>
+        <v>92.45999999999999</v>
       </c>
       <c r="L16" t="n">
         <v>6.4</v>
@@ -1362,7 +1553,19 @@
         <v>1</v>
       </c>
       <c r="Q16" t="n">
-        <v>157</v>
+        <v>158</v>
+      </c>
+      <c r="R16" s="3" t="n">
+        <v>45043</v>
+      </c>
+      <c r="S16" t="b">
+        <v>1</v>
+      </c>
+      <c r="T16" t="n">
+        <v>5</v>
+      </c>
+      <c r="U16" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="17">
@@ -1389,28 +1592,28 @@
         <v>13.52</v>
       </c>
       <c r="G17" s="1" t="n">
-        <v>45167.55208333334</v>
+        <v>45168.38541666666</v>
       </c>
       <c r="H17" t="n">
-        <v>50.27</v>
+        <v>52.49</v>
       </c>
       <c r="I17" t="n">
         <v>52.24832644907642</v>
       </c>
       <c r="J17" s="2" t="n">
-        <v>15</v>
+        <v>15.83333333333333</v>
       </c>
       <c r="K17" t="n">
-        <v>-2.51</v>
+        <v>-7.04</v>
       </c>
       <c r="L17" t="n">
-        <v>5.93</v>
+        <v>9.050000000000001</v>
       </c>
       <c r="M17" t="n">
         <v>3.43</v>
       </c>
       <c r="N17" t="n">
-        <v>3.79</v>
+        <v>3.92</v>
       </c>
       <c r="O17" t="n">
         <v>-4.87</v>
@@ -1419,7 +1622,19 @@
         <v>1</v>
       </c>
       <c r="Q17" t="n">
-        <v>21</v>
+        <v>22</v>
+      </c>
+      <c r="R17" s="3" t="n">
+        <v>45169</v>
+      </c>
+      <c r="S17" t="b">
+        <v>0</v>
+      </c>
+      <c r="T17" t="n">
+        <v>1</v>
+      </c>
+      <c r="U17" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -1446,19 +1661,19 @@
         <v>9.869999999999999</v>
       </c>
       <c r="G18" s="1" t="n">
-        <v>45191.38541666666</v>
+        <v>45191.55208333334</v>
       </c>
       <c r="H18" t="n">
-        <v>48.05</v>
+        <v>47.07</v>
       </c>
       <c r="I18" t="n">
         <v>47.50749528142311</v>
       </c>
       <c r="J18" s="2" t="n">
-        <v>23</v>
+        <v>23.16666666666667</v>
       </c>
       <c r="K18" t="n">
-        <v>-8.460000000000001</v>
+        <v>-10.33</v>
       </c>
       <c r="L18" t="n">
         <v>11.64</v>
@@ -1476,7 +1691,19 @@
         <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>33</v>
+        <v>34</v>
+      </c>
+      <c r="R18" s="3" t="n">
+        <v>45169</v>
+      </c>
+      <c r="S18" t="b">
+        <v>1</v>
+      </c>
+      <c r="T18" t="n">
+        <v>2</v>
+      </c>
+      <c r="U18" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="19">
@@ -1503,28 +1730,28 @@
         <v>9.73</v>
       </c>
       <c r="G19" s="1" t="n">
-        <v>45204.55208333334</v>
+        <v>45205.38541666666</v>
       </c>
       <c r="H19" t="n">
-        <v>48.89</v>
+        <v>51.55</v>
       </c>
       <c r="I19" t="n">
         <v>51.1631186110472</v>
       </c>
       <c r="J19" s="2" t="n">
-        <v>13</v>
+        <v>13.83333333333333</v>
       </c>
       <c r="K19" t="n">
-        <v>-3.87</v>
+        <v>-9.52</v>
       </c>
       <c r="L19" t="n">
-        <v>7.86</v>
+        <v>10.88</v>
       </c>
       <c r="M19" t="n">
         <v>2.78</v>
       </c>
       <c r="N19" t="n">
-        <v>2.41</v>
+        <v>5.85</v>
       </c>
       <c r="O19" t="n">
         <v>-3.05</v>
@@ -1533,7 +1760,19 @@
         <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>17</v>
+        <v>18</v>
+      </c>
+      <c r="R19" s="3" t="n">
+        <v>45197</v>
+      </c>
+      <c r="S19" t="b">
+        <v>1</v>
+      </c>
+      <c r="T19" t="n">
+        <v>2</v>
+      </c>
+      <c r="U19" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="20">
@@ -1560,28 +1799,28 @@
         <v>10.37</v>
       </c>
       <c r="G20" s="1" t="n">
-        <v>45222.55208333334</v>
+        <v>45224.38541666666</v>
       </c>
       <c r="H20" t="n">
-        <v>51.36</v>
+        <v>46.92</v>
       </c>
       <c r="I20" t="n">
         <v>49.32521971962678</v>
       </c>
       <c r="J20" s="2" t="n">
-        <v>17.16666666666667</v>
+        <v>19</v>
       </c>
       <c r="K20" t="n">
-        <v>-0.37</v>
+        <v>-8.98</v>
       </c>
       <c r="L20" t="n">
-        <v>5.35</v>
+        <v>9.369999999999999</v>
       </c>
       <c r="M20" t="n">
-        <v>1.14</v>
+        <v>1.54</v>
       </c>
       <c r="N20" t="n">
-        <v>2.67</v>
+        <v>3.08</v>
       </c>
       <c r="O20" t="n">
         <v>5.85</v>
@@ -1590,7 +1829,19 @@
         <v>1</v>
       </c>
       <c r="Q20" t="n">
-        <v>24</v>
+        <v>25</v>
+      </c>
+      <c r="R20" s="3" t="n">
+        <v>45225</v>
+      </c>
+      <c r="S20" t="b">
+        <v>0</v>
+      </c>
+      <c r="T20" t="n">
+        <v>1</v>
+      </c>
+      <c r="U20" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -1617,22 +1868,22 @@
         <v>18.61</v>
       </c>
       <c r="G21" s="1" t="n">
-        <v>45229.38541666666</v>
+        <v>45229.55208333334</v>
       </c>
       <c r="H21" t="n">
-        <v>53.43</v>
+        <v>55.69</v>
       </c>
       <c r="I21" t="n">
         <v>55.18569039816877</v>
       </c>
       <c r="J21" s="2" t="n">
-        <v>5</v>
+        <v>5.166666666666667</v>
       </c>
       <c r="K21" t="n">
-        <v>-13.87</v>
+        <v>-18.69</v>
       </c>
       <c r="L21" t="n">
-        <v>16.28</v>
+        <v>19.22</v>
       </c>
       <c r="M21" t="n">
         <v>1.34</v>
@@ -1647,7 +1898,19 @@
         <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>7</v>
+        <v>8</v>
+      </c>
+      <c r="R21" s="3" t="n">
+        <v>45225</v>
+      </c>
+      <c r="S21" t="b">
+        <v>1</v>
+      </c>
+      <c r="T21" t="n">
+        <v>2</v>
+      </c>
+      <c r="U21" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="22">
@@ -1674,19 +1937,19 @@
         <v>17.22</v>
       </c>
       <c r="G22" s="1" t="n">
-        <v>45300.55208333334</v>
+        <v>45301.38541666666</v>
       </c>
       <c r="H22" t="n">
-        <v>117.79</v>
+        <v>108.23</v>
       </c>
       <c r="I22" t="n">
         <v>113.9979034123171</v>
       </c>
       <c r="J22" s="2" t="n">
-        <v>71</v>
+        <v>71.83333333333333</v>
       </c>
       <c r="K22" t="n">
-        <v>111.51</v>
+        <v>94.34</v>
       </c>
       <c r="L22" t="n">
         <v>8.130000000000001</v>
@@ -1704,7 +1967,19 @@
         <v>1</v>
       </c>
       <c r="Q22" t="n">
-        <v>98</v>
+        <v>99</v>
+      </c>
+      <c r="R22" s="3" t="n">
+        <v>45260</v>
+      </c>
+      <c r="S22" t="b">
+        <v>1</v>
+      </c>
+      <c r="T22" t="n">
+        <v>3</v>
+      </c>
+      <c r="U22" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="23">
@@ -1731,19 +2006,19 @@
         <v>20.61</v>
       </c>
       <c r="G23" s="1" t="n">
-        <v>45320.38541666666</v>
+        <v>45320.55208333334</v>
       </c>
       <c r="H23" t="n">
-        <v>118.78</v>
+        <v>120.65</v>
       </c>
       <c r="I23" t="n">
         <v>119.6011149571323</v>
       </c>
       <c r="J23" s="2" t="n">
-        <v>19</v>
+        <v>19.16666666666667</v>
       </c>
       <c r="K23" t="n">
-        <v>-9.75</v>
+        <v>-11.48</v>
       </c>
       <c r="L23" t="n">
         <v>12.48</v>
@@ -1761,7 +2036,19 @@
         <v>0</v>
       </c>
       <c r="Q23" t="n">
-        <v>25</v>
+        <v>26</v>
+      </c>
+      <c r="R23" s="3" t="n">
+        <v>45316</v>
+      </c>
+      <c r="S23" t="b">
+        <v>1</v>
+      </c>
+      <c r="T23" t="n">
+        <v>2</v>
+      </c>
+      <c r="U23" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="24">
@@ -1788,19 +2075,19 @@
         <v>12.66</v>
       </c>
       <c r="G24" s="1" t="n">
-        <v>45334.38541666666</v>
+        <v>45334.55208333334</v>
       </c>
       <c r="H24" t="n">
-        <v>124.35</v>
+        <v>121</v>
       </c>
       <c r="I24" t="n">
         <v>121.9687679130789</v>
       </c>
       <c r="J24" s="2" t="n">
-        <v>13.83333333333333</v>
+        <v>14</v>
       </c>
       <c r="K24" t="n">
-        <v>3.07</v>
+        <v>0.29</v>
       </c>
       <c r="L24" t="n">
         <v>5.72</v>
@@ -1818,7 +2105,19 @@
         <v>1</v>
       </c>
       <c r="Q24" t="n">
-        <v>20</v>
+        <v>21</v>
+      </c>
+      <c r="R24" s="3" t="n">
+        <v>45351</v>
+      </c>
+      <c r="S24" t="b">
+        <v>0</v>
+      </c>
+      <c r="T24" t="n">
+        <v>1</v>
+      </c>
+      <c r="U24" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="25">
@@ -1845,22 +2144,22 @@
         <v>18.22</v>
       </c>
       <c r="G25" s="1" t="n">
-        <v>45337.55208333334</v>
+        <v>45338.38541666666</v>
       </c>
       <c r="H25" t="n">
-        <v>142.34</v>
+        <v>145.54</v>
       </c>
       <c r="I25" t="n">
         <v>143.048561285006</v>
       </c>
       <c r="J25" s="2" t="n">
-        <v>3</v>
+        <v>3.833333333333333</v>
       </c>
       <c r="K25" t="n">
-        <v>-17.64</v>
+        <v>-20.28</v>
       </c>
       <c r="L25" t="n">
-        <v>17.64</v>
+        <v>21.79</v>
       </c>
       <c r="M25" t="n">
         <v>1.83</v>
@@ -1875,7 +2174,19 @@
         <v>0</v>
       </c>
       <c r="Q25" t="n">
-        <v>7</v>
+        <v>8</v>
+      </c>
+      <c r="R25" s="3" t="n">
+        <v>45351</v>
+      </c>
+      <c r="S25" t="b">
+        <v>0</v>
+      </c>
+      <c r="T25" t="n">
+        <v>1</v>
+      </c>
+      <c r="U25" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="26">
@@ -1902,28 +2213,28 @@
         <v>14.72</v>
       </c>
       <c r="G26" s="1" t="n">
-        <v>45352.38541666666</v>
+        <v>45355.38541666666</v>
       </c>
       <c r="H26" t="n">
-        <v>147.02</v>
+        <v>136.18</v>
       </c>
       <c r="I26" t="n">
         <v>138.6905941696622</v>
       </c>
       <c r="J26" s="2" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="K26" t="n">
-        <v>1.02</v>
+        <v>-6.43</v>
       </c>
       <c r="L26" t="n">
-        <v>3.28</v>
+        <v>6.43</v>
       </c>
       <c r="M26" t="n">
-        <v>0.33</v>
+        <v>7.37</v>
       </c>
       <c r="N26" t="n">
-        <v>4.37</v>
+        <v>7.37</v>
       </c>
       <c r="O26" t="n">
         <v>2.66</v>
@@ -1932,7 +2243,19 @@
         <v>0</v>
       </c>
       <c r="Q26" t="n">
-        <v>21</v>
+        <v>22</v>
+      </c>
+      <c r="R26" s="3" t="n">
+        <v>45351</v>
+      </c>
+      <c r="S26" t="b">
+        <v>1</v>
+      </c>
+      <c r="T26" t="n">
+        <v>2</v>
+      </c>
+      <c r="U26" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="27">
@@ -1959,19 +2282,19 @@
         <v>15.52</v>
       </c>
       <c r="G27" s="1" t="n">
-        <v>45377.55208333334</v>
+        <v>45378.38541666666</v>
       </c>
       <c r="H27" t="n">
-        <v>124.4</v>
+        <v>129.62</v>
       </c>
       <c r="I27" t="n">
         <v>125.8988018110714</v>
       </c>
       <c r="J27" s="2" t="n">
-        <v>22.16666666666667</v>
+        <v>23</v>
       </c>
       <c r="K27" t="n">
-        <v>8.65</v>
+        <v>4.82</v>
       </c>
       <c r="L27" t="n">
         <v>0.76</v>
@@ -1989,7 +2312,19 @@
         <v>1</v>
       </c>
       <c r="Q27" t="n">
-        <v>30</v>
+        <v>31</v>
+      </c>
+      <c r="R27" s="3" t="n">
+        <v>45379</v>
+      </c>
+      <c r="S27" t="b">
+        <v>0</v>
+      </c>
+      <c r="T27" t="n">
+        <v>1</v>
+      </c>
+      <c r="U27" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="28">
@@ -2016,19 +2351,19 @@
         <v>12.99</v>
       </c>
       <c r="G28" s="1" t="n">
-        <v>45418.55208333334</v>
+        <v>45419.38541666666</v>
       </c>
       <c r="H28" t="n">
-        <v>150.03</v>
+        <v>137.9</v>
       </c>
       <c r="I28" t="n">
         <v>140.8814515901686</v>
       </c>
       <c r="J28" s="2" t="n">
-        <v>40.16666666666666</v>
+        <v>41</v>
       </c>
       <c r="K28" t="n">
-        <v>15.75</v>
+        <v>6.39</v>
       </c>
       <c r="L28" t="n">
         <v>3.99</v>
@@ -2037,7 +2372,7 @@
         <v>4.42</v>
       </c>
       <c r="N28" t="n">
-        <v>3.53</v>
+        <v>6.54</v>
       </c>
       <c r="O28" t="n">
         <v>4.99</v>
@@ -2046,7 +2381,19 @@
         <v>1</v>
       </c>
       <c r="Q28" t="n">
-        <v>50</v>
+        <v>51</v>
+      </c>
+      <c r="R28" s="3" t="n">
+        <v>45379</v>
+      </c>
+      <c r="S28" t="b">
+        <v>1</v>
+      </c>
+      <c r="T28" t="n">
+        <v>3</v>
+      </c>
+      <c r="U28" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="29">
@@ -2073,22 +2420,22 @@
         <v>18.39</v>
       </c>
       <c r="G29" s="1" t="n">
-        <v>45428.38541666666</v>
+        <v>45428.55208333334</v>
       </c>
       <c r="H29" t="n">
-        <v>148.01</v>
+        <v>151.61</v>
       </c>
       <c r="I29" t="n">
         <v>148.8965266776997</v>
       </c>
       <c r="J29" s="2" t="n">
-        <v>9</v>
+        <v>9.166666666666666</v>
       </c>
       <c r="K29" t="n">
-        <v>-7.33</v>
+        <v>-9.94</v>
       </c>
       <c r="L29" t="n">
-        <v>9.76</v>
+        <v>9.94</v>
       </c>
       <c r="M29" t="n">
         <v>2.34</v>
@@ -2103,7 +2450,19 @@
         <v>1</v>
       </c>
       <c r="Q29" t="n">
-        <v>15</v>
+        <v>16</v>
+      </c>
+      <c r="R29" s="3" t="n">
+        <v>45442</v>
+      </c>
+      <c r="S29" t="b">
+        <v>0</v>
+      </c>
+      <c r="T29" t="n">
+        <v>1</v>
+      </c>
+      <c r="U29" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="30">
@@ -2130,28 +2489,28 @@
         <v>11.52</v>
       </c>
       <c r="G30" s="1" t="n">
-        <v>45439.55208333334</v>
+        <v>45440.38541666666</v>
       </c>
       <c r="H30" t="n">
-        <v>161.46</v>
+        <v>145.64</v>
       </c>
       <c r="I30" t="n">
         <v>146.8473668240844</v>
       </c>
       <c r="J30" s="2" t="n">
-        <v>11</v>
+        <v>11.83333333333333</v>
       </c>
       <c r="K30" t="n">
-        <v>6.5</v>
+        <v>-3.94</v>
       </c>
       <c r="L30" t="n">
-        <v>3.61</v>
+        <v>3.94</v>
       </c>
       <c r="M30" t="n">
-        <v>-0</v>
+        <v>5.37</v>
       </c>
       <c r="N30" t="n">
-        <v>3.02</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="O30" t="n">
         <v>10.25</v>
@@ -2160,7 +2519,19 @@
         <v>1</v>
       </c>
       <c r="Q30" t="n">
-        <v>14</v>
+        <v>15</v>
+      </c>
+      <c r="R30" s="3" t="n">
+        <v>45442</v>
+      </c>
+      <c r="S30" t="b">
+        <v>0</v>
+      </c>
+      <c r="T30" t="n">
+        <v>1</v>
+      </c>
+      <c r="U30" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="31">
@@ -2187,28 +2558,28 @@
         <v>18.09</v>
       </c>
       <c r="G31" s="1" t="n">
-        <v>45476.55208333334</v>
+        <v>45477.38541666666</v>
       </c>
       <c r="H31" t="n">
-        <v>140.21</v>
+        <v>156.9</v>
       </c>
       <c r="I31" t="n">
         <v>149.1892260753262</v>
       </c>
       <c r="J31" s="2" t="n">
-        <v>36.16666666666666</v>
+        <v>37</v>
       </c>
       <c r="K31" t="n">
-        <v>3.73</v>
+        <v>-7.73</v>
       </c>
       <c r="L31" t="n">
-        <v>6.74</v>
+        <v>11</v>
       </c>
       <c r="M31" t="n">
         <v>6.8</v>
       </c>
       <c r="N31" t="n">
-        <v>4.93</v>
+        <v>10.48</v>
       </c>
       <c r="O31" t="n">
         <v>-9.800000000000001</v>
@@ -2217,7 +2588,19 @@
         <v>1</v>
       </c>
       <c r="Q31" t="n">
-        <v>52</v>
+        <v>53</v>
+      </c>
+      <c r="R31" s="3" t="n">
+        <v>45442</v>
+      </c>
+      <c r="S31" t="b">
+        <v>1</v>
+      </c>
+      <c r="T31" t="n">
+        <v>3</v>
+      </c>
+      <c r="U31" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="32">
@@ -2244,25 +2627,25 @@
         <v>11.51</v>
       </c>
       <c r="G32" s="1" t="n">
-        <v>45492.55208333334</v>
+        <v>45495.38541666666</v>
       </c>
       <c r="H32" t="n">
-        <v>151.01</v>
+        <v>147.81</v>
       </c>
       <c r="I32" t="n">
         <v>149.60860229035</v>
       </c>
       <c r="J32" s="2" t="n">
-        <v>15.16666666666667</v>
+        <v>18</v>
       </c>
       <c r="K32" t="n">
-        <v>-3.75</v>
+        <v>-5.79</v>
       </c>
       <c r="L32" t="n">
         <v>7.2</v>
       </c>
       <c r="M32" t="n">
-        <v>0.66</v>
+        <v>1.3</v>
       </c>
       <c r="N32" t="n">
         <v>4.25</v>
@@ -2274,7 +2657,19 @@
         <v>1</v>
       </c>
       <c r="Q32" t="n">
-        <v>22</v>
+        <v>23</v>
+      </c>
+      <c r="R32" s="3" t="n">
+        <v>45498</v>
+      </c>
+      <c r="S32" t="b">
+        <v>0</v>
+      </c>
+      <c r="T32" t="n">
+        <v>1</v>
+      </c>
+      <c r="U32" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="33">
@@ -2301,22 +2696,22 @@
         <v>15.99</v>
       </c>
       <c r="G33" s="1" t="n">
-        <v>45498.55208333334</v>
+        <v>45499.38541666666</v>
       </c>
       <c r="H33" t="n">
-        <v>161.56</v>
+        <v>167.49</v>
       </c>
       <c r="I33" t="n">
         <v>165.6878578221234</v>
       </c>
       <c r="J33" s="2" t="n">
-        <v>3.166666666666667</v>
+        <v>4</v>
       </c>
       <c r="K33" t="n">
-        <v>-9.300000000000001</v>
+        <v>-13.31</v>
       </c>
       <c r="L33" t="n">
-        <v>12.71</v>
+        <v>16.04</v>
       </c>
       <c r="M33" t="n">
         <v>1.83</v>
@@ -2331,7 +2726,19 @@
         <v>0</v>
       </c>
       <c r="Q33" t="n">
-        <v>8</v>
+        <v>9</v>
+      </c>
+      <c r="R33" s="3" t="n">
+        <v>45498</v>
+      </c>
+      <c r="S33" t="b">
+        <v>1</v>
+      </c>
+      <c r="T33" t="n">
+        <v>2</v>
+      </c>
+      <c r="U33" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="34">
@@ -2358,19 +2765,19 @@
         <v>14.11</v>
       </c>
       <c r="G34" s="1" t="n">
-        <v>45568.55208333334</v>
+        <v>45569.38541666666</v>
       </c>
       <c r="H34" t="n">
-        <v>226.22</v>
+        <v>219.84</v>
       </c>
       <c r="I34" t="n">
         <v>223.6709444431942</v>
       </c>
       <c r="J34" s="2" t="n">
-        <v>69.16666666666667</v>
+        <v>70</v>
       </c>
       <c r="K34" t="n">
-        <v>35.06</v>
+        <v>31.26</v>
       </c>
       <c r="L34" t="n">
         <v>3.7</v>
@@ -2388,7 +2795,19 @@
         <v>0</v>
       </c>
       <c r="Q34" t="n">
-        <v>96</v>
+        <v>97</v>
+      </c>
+      <c r="R34" s="3" t="n">
+        <v>45533</v>
+      </c>
+      <c r="S34" t="b">
+        <v>1</v>
+      </c>
+      <c r="T34" t="n">
+        <v>3</v>
+      </c>
+      <c r="U34" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="35">
@@ -2415,19 +2834,19 @@
         <v>11.08</v>
       </c>
       <c r="G35" s="1" t="n">
-        <v>45628.55208333334</v>
+        <v>45629.38541666666</v>
       </c>
       <c r="H35" t="n">
-        <v>197.32</v>
+        <v>202.89</v>
       </c>
       <c r="I35" t="n">
         <v>200.3132872296436</v>
       </c>
       <c r="J35" s="2" t="n">
-        <v>59.16666666666666</v>
+        <v>60</v>
       </c>
       <c r="K35" t="n">
-        <v>10.24</v>
+        <v>7.71</v>
       </c>
       <c r="L35" t="n">
         <v>3.53</v>
@@ -2445,7 +2864,19 @@
         <v>0</v>
       </c>
       <c r="Q35" t="n">
-        <v>79</v>
+        <v>80</v>
+      </c>
+      <c r="R35" s="3" t="n">
+        <v>45596</v>
+      </c>
+      <c r="S35" t="b">
+        <v>1</v>
+      </c>
+      <c r="T35" t="n">
+        <v>3</v>
+      </c>
+      <c r="U35" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="36">
@@ -2472,22 +2903,22 @@
         <v>10.23</v>
       </c>
       <c r="G36" s="1" t="n">
-        <v>45643.38541666666</v>
+        <v>45643.55208333334</v>
       </c>
       <c r="H36" t="n">
-        <v>190.74</v>
+        <v>189.45</v>
       </c>
       <c r="I36" t="n">
         <v>190.4173097520033</v>
       </c>
       <c r="J36" s="2" t="n">
-        <v>14</v>
+        <v>14.16666666666667</v>
       </c>
       <c r="K36" t="n">
-        <v>-5.99</v>
+        <v>-6.62</v>
       </c>
       <c r="L36" t="n">
-        <v>6.35</v>
+        <v>6.83</v>
       </c>
       <c r="M36" t="n">
         <v>0.74</v>
@@ -2502,7 +2933,19 @@
         <v>0</v>
       </c>
       <c r="Q36" t="n">
-        <v>21</v>
+        <v>22</v>
+      </c>
+      <c r="R36" s="3" t="n">
+        <v>45652</v>
+      </c>
+      <c r="S36" t="b">
+        <v>0</v>
+      </c>
+      <c r="T36" t="n">
+        <v>1</v>
+      </c>
+      <c r="U36" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="37">
@@ -2529,19 +2972,19 @@
         <v>7.7</v>
       </c>
       <c r="G37" s="1" t="n">
-        <v>45672.55208333334</v>
+        <v>45673.38541666666</v>
       </c>
       <c r="H37" t="n">
-        <v>160.19</v>
+        <v>165.47</v>
       </c>
       <c r="I37" t="n">
         <v>162.3073102069343</v>
       </c>
       <c r="J37" s="2" t="n">
-        <v>29</v>
+        <v>29.83333333333333</v>
       </c>
       <c r="K37" t="n">
-        <v>15.44</v>
+        <v>12.66</v>
       </c>
       <c r="L37" t="n">
         <v>1.62</v>
@@ -2559,7 +3002,19 @@
         <v>0</v>
       </c>
       <c r="Q37" t="n">
-        <v>41</v>
+        <v>42</v>
+      </c>
+      <c r="R37" s="3" t="n">
+        <v>45652</v>
+      </c>
+      <c r="S37" t="b">
+        <v>1</v>
+      </c>
+      <c r="T37" t="n">
+        <v>2</v>
+      </c>
+      <c r="U37" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="38">
@@ -2586,22 +3041,22 @@
         <v>10.73</v>
       </c>
       <c r="G38" s="1" t="n">
-        <v>45679.55208333334</v>
+        <v>45680.38541666666</v>
       </c>
       <c r="H38" t="n">
-        <v>153.53</v>
+        <v>149.42</v>
       </c>
       <c r="I38" t="n">
         <v>150.2897424010533</v>
       </c>
       <c r="J38" s="2" t="n">
-        <v>6.166666666666667</v>
+        <v>7</v>
       </c>
       <c r="K38" t="n">
-        <v>-7.22</v>
+        <v>-9.699999999999999</v>
       </c>
       <c r="L38" t="n">
-        <v>7.66</v>
+        <v>10.76</v>
       </c>
       <c r="M38" t="n">
         <v>0.7</v>
@@ -2616,7 +3071,19 @@
         <v>0</v>
       </c>
       <c r="Q38" t="n">
-        <v>10</v>
+        <v>11</v>
+      </c>
+      <c r="R38" s="3" t="n">
+        <v>45687</v>
+      </c>
+      <c r="S38" t="b">
+        <v>0</v>
+      </c>
+      <c r="T38" t="n">
+        <v>1</v>
+      </c>
+      <c r="U38" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="39">
@@ -2643,28 +3110,28 @@
         <v>12.78</v>
       </c>
       <c r="G39" s="1" t="n">
-        <v>45685.55208333334</v>
+        <v>45686.38541666666</v>
       </c>
       <c r="H39" t="n">
-        <v>132.97</v>
+        <v>156.6</v>
       </c>
       <c r="I39" t="n">
         <v>151.2554239985934</v>
       </c>
       <c r="J39" s="2" t="n">
-        <v>5.166666666666667</v>
+        <v>6</v>
       </c>
       <c r="K39" t="n">
-        <v>11.01</v>
+        <v>-4.81</v>
       </c>
       <c r="L39" t="n">
-        <v>3.25</v>
+        <v>6.81</v>
       </c>
       <c r="M39" t="n">
-        <v>0.06</v>
+        <v>2.3</v>
       </c>
       <c r="N39" t="n">
-        <v>0</v>
+        <v>20.03</v>
       </c>
       <c r="O39" t="n">
         <v>-3.73</v>
@@ -2673,7 +3140,19 @@
         <v>0</v>
       </c>
       <c r="Q39" t="n">
-        <v>8</v>
+        <v>9</v>
+      </c>
+      <c r="R39" s="3" t="n">
+        <v>45687</v>
+      </c>
+      <c r="S39" t="b">
+        <v>0</v>
+      </c>
+      <c r="T39" t="n">
+        <v>1</v>
+      </c>
+      <c r="U39" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="40">
@@ -2700,28 +3179,28 @@
         <v>21.04</v>
       </c>
       <c r="G40" s="1" t="n">
-        <v>45713.55208333334</v>
+        <v>45715.38541666666</v>
       </c>
       <c r="H40" t="n">
-        <v>166</v>
+        <v>152.89</v>
       </c>
       <c r="I40" t="n">
         <v>154.1778151376494</v>
       </c>
       <c r="J40" s="2" t="n">
-        <v>27.16666666666667</v>
+        <v>29</v>
       </c>
       <c r="K40" t="n">
-        <v>6</v>
+        <v>-2.37</v>
       </c>
       <c r="L40" t="n">
         <v>13.35</v>
       </c>
       <c r="M40" t="n">
-        <v>2.32</v>
+        <v>2.85</v>
       </c>
       <c r="N40" t="n">
-        <v>5.93</v>
+        <v>8.27</v>
       </c>
       <c r="O40" t="n">
         <v>20.03</v>
@@ -2730,7 +3209,19 @@
         <v>1</v>
       </c>
       <c r="Q40" t="n">
-        <v>42</v>
+        <v>43</v>
+      </c>
+      <c r="R40" s="3" t="n">
+        <v>45687</v>
+      </c>
+      <c r="S40" t="b">
+        <v>1</v>
+      </c>
+      <c r="T40" t="n">
+        <v>2</v>
+      </c>
+      <c r="U40" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="41">
@@ -2757,28 +3248,28 @@
         <v>15.46</v>
       </c>
       <c r="G41" s="1" t="n">
-        <v>45722.55208333334</v>
+        <v>45723.38541666666</v>
       </c>
       <c r="H41" t="n">
-        <v>150.42</v>
+        <v>169.93</v>
       </c>
       <c r="I41" t="n">
         <v>162.8762456056544</v>
       </c>
       <c r="J41" s="2" t="n">
-        <v>7.166666666666667</v>
+        <v>8</v>
       </c>
       <c r="K41" t="n">
-        <v>1.62</v>
+        <v>-11.15</v>
       </c>
       <c r="L41" t="n">
-        <v>6.53</v>
+        <v>11.88</v>
       </c>
       <c r="M41" t="n">
         <v>1.85</v>
       </c>
       <c r="N41" t="n">
-        <v>6.41</v>
+        <v>11.73</v>
       </c>
       <c r="O41" t="n">
         <v>-8.27</v>
@@ -2787,7 +3278,19 @@
         <v>1</v>
       </c>
       <c r="Q41" t="n">
-        <v>12</v>
+        <v>13</v>
+      </c>
+      <c r="R41" s="3" t="n">
+        <v>45743</v>
+      </c>
+      <c r="S41" t="b">
+        <v>0</v>
+      </c>
+      <c r="T41" t="n">
+        <v>1</v>
+      </c>
+      <c r="U41" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="42">
@@ -2814,19 +3317,19 @@
         <v>19.37</v>
       </c>
       <c r="G42" s="1" t="n">
-        <v>45742.55208333334</v>
+        <v>45743.38541666666</v>
       </c>
       <c r="H42" t="n">
-        <v>157.62</v>
+        <v>155.61</v>
       </c>
       <c r="I42" t="n">
         <v>157.2738258177605</v>
       </c>
       <c r="J42" s="2" t="n">
-        <v>19.16666666666667</v>
+        <v>20</v>
       </c>
       <c r="K42" t="n">
-        <v>-7.24</v>
+        <v>-8.43</v>
       </c>
       <c r="L42" t="n">
         <v>11.46</v>
@@ -2844,7 +3347,19 @@
         <v>1</v>
       </c>
       <c r="Q42" t="n">
-        <v>26</v>
+        <v>27</v>
+      </c>
+      <c r="R42" s="3" t="n">
+        <v>45743</v>
+      </c>
+      <c r="S42" t="b">
+        <v>0</v>
+      </c>
+      <c r="T42" t="n">
+        <v>1</v>
+      </c>
+      <c r="U42" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="43">
@@ -2871,19 +3386,19 @@
         <v>10.1</v>
       </c>
       <c r="G43" s="1" t="n">
-        <v>45758.55208333334</v>
+        <v>45762.38541666666</v>
       </c>
       <c r="H43" t="n">
-        <v>149.63</v>
+        <v>158.7</v>
       </c>
       <c r="I43" t="n">
         <v>155.7341836021388</v>
       </c>
       <c r="J43" s="2" t="n">
-        <v>15.16666666666667</v>
+        <v>19</v>
       </c>
       <c r="K43" t="n">
-        <v>3.84</v>
+        <v>-1.99</v>
       </c>
       <c r="L43" t="n">
         <v>8.039999999999999</v>
@@ -2901,7 +3416,19 @@
         <v>0</v>
       </c>
       <c r="Q43" t="n">
-        <v>18</v>
+        <v>19</v>
+      </c>
+      <c r="R43" s="3" t="n">
+        <v>45771</v>
+      </c>
+      <c r="S43" t="b">
+        <v>0</v>
+      </c>
+      <c r="T43" t="n">
+        <v>1</v>
+      </c>
+      <c r="U43" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="44">
@@ -2928,19 +3455,19 @@
         <v>13.25</v>
       </c>
       <c r="G44" s="1" t="n">
-        <v>45783.38541666666</v>
+        <v>45783.55208333334</v>
       </c>
       <c r="H44" t="n">
-        <v>165.14</v>
+        <v>161.45</v>
       </c>
       <c r="I44" t="n">
         <v>162.4551660099852</v>
       </c>
       <c r="J44" s="2" t="n">
-        <v>21</v>
+        <v>21.16666666666667</v>
       </c>
       <c r="K44" t="n">
-        <v>4.06</v>
+        <v>1.73</v>
       </c>
       <c r="L44" t="n">
         <v>3.72</v>
@@ -2958,7 +3485,19 @@
         <v>1</v>
       </c>
       <c r="Q44" t="n">
-        <v>27</v>
+        <v>28</v>
+      </c>
+      <c r="R44" s="3" t="n">
+        <v>45771</v>
+      </c>
+      <c r="S44" t="b">
+        <v>1</v>
+      </c>
+      <c r="T44" t="n">
+        <v>2</v>
+      </c>
+      <c r="U44" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="45">
@@ -2985,22 +3524,22 @@
         <v>10.14</v>
       </c>
       <c r="G45" s="1" t="n">
-        <v>45790.55208333334</v>
+        <v>45791.38541666666</v>
       </c>
       <c r="H45" t="n">
-        <v>167.08</v>
+        <v>171.92</v>
       </c>
       <c r="I45" t="n">
         <v>169.7928347922792</v>
       </c>
       <c r="J45" s="2" t="n">
-        <v>7</v>
+        <v>7.833333333333333</v>
       </c>
       <c r="K45" t="n">
-        <v>-3.49</v>
+        <v>-6.48</v>
       </c>
       <c r="L45" t="n">
-        <v>4.65</v>
+        <v>7.3</v>
       </c>
       <c r="M45" t="n">
         <v>5.36</v>
@@ -3015,7 +3554,19 @@
         <v>1</v>
       </c>
       <c r="Q45" t="n">
-        <v>11</v>
+        <v>12</v>
+      </c>
+      <c r="R45" s="3" t="n">
+        <v>45806</v>
+      </c>
+      <c r="S45" t="b">
+        <v>0</v>
+      </c>
+      <c r="T45" t="n">
+        <v>1</v>
+      </c>
+      <c r="U45" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="46">
@@ -3042,19 +3593,19 @@
         <v>9.779999999999999</v>
       </c>
       <c r="G46" s="1" t="n">
-        <v>45810.55208333334</v>
+        <v>45811.38541666666</v>
       </c>
       <c r="H46" t="n">
-        <v>182.45</v>
+        <v>179.96</v>
       </c>
       <c r="I46" t="n">
         <v>180.1899509442174</v>
       </c>
       <c r="J46" s="2" t="n">
-        <v>19.16666666666667</v>
+        <v>20</v>
       </c>
       <c r="K46" t="n">
-        <v>6.12</v>
+        <v>4.68</v>
       </c>
       <c r="L46" t="n">
         <v>2.53</v>
@@ -3072,7 +3623,19 @@
         <v>0</v>
       </c>
       <c r="Q46" t="n">
-        <v>28</v>
+        <v>29</v>
+      </c>
+      <c r="R46" s="3" t="n">
+        <v>45806</v>
+      </c>
+      <c r="S46" t="b">
+        <v>1</v>
+      </c>
+      <c r="T46" t="n">
+        <v>2</v>
+      </c>
+      <c r="U46" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="47">
@@ -3099,19 +3662,19 @@
         <v>11.02</v>
       </c>
       <c r="G47" s="1" t="n">
-        <v>45840.38541666666</v>
+        <v>45840.55208333334</v>
       </c>
       <c r="H47" t="n">
-        <v>172.9</v>
+        <v>174.87</v>
       </c>
       <c r="I47" t="n">
         <v>174.5639071803827</v>
       </c>
       <c r="J47" s="2" t="n">
-        <v>29</v>
+        <v>29.16666666666667</v>
       </c>
       <c r="K47" t="n">
-        <v>3.92</v>
+        <v>2.83</v>
       </c>
       <c r="L47" t="n">
         <v>4.07</v>
@@ -3129,7 +3692,19 @@
         <v>0</v>
       </c>
       <c r="Q47" t="n">
-        <v>43</v>
+        <v>44</v>
+      </c>
+      <c r="R47" s="3" t="n">
+        <v>45834</v>
+      </c>
+      <c r="S47" t="b">
+        <v>1</v>
+      </c>
+      <c r="T47" t="n">
+        <v>2</v>
+      </c>
+      <c r="U47" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="48">
@@ -3156,22 +3731,22 @@
         <v>6.03</v>
       </c>
       <c r="G48" s="1" t="n">
-        <v>45853.38541666666</v>
+        <v>45853.55208333334</v>
       </c>
       <c r="H48" t="n">
-        <v>170.53</v>
+        <v>162.64</v>
       </c>
       <c r="I48" t="n">
         <v>168.4407355375013</v>
       </c>
       <c r="J48" s="2" t="n">
-        <v>12.83333333333333</v>
+        <v>13</v>
       </c>
       <c r="K48" t="n">
-        <v>-2.48</v>
+        <v>-6.99</v>
       </c>
       <c r="L48" t="n">
-        <v>2.72</v>
+        <v>7.67</v>
       </c>
       <c r="M48" t="n">
         <v>0.51</v>
@@ -3186,7 +3761,19 @@
         <v>0</v>
       </c>
       <c r="Q48" t="n">
-        <v>18</v>
+        <v>19</v>
+      </c>
+      <c r="R48" s="3" t="n">
+        <v>45869</v>
+      </c>
+      <c r="S48" t="b">
+        <v>0</v>
+      </c>
+      <c r="T48" t="n">
+        <v>1</v>
+      </c>
+      <c r="U48" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="49">
@@ -3213,19 +3800,19 @@
         <v>8.710000000000001</v>
       </c>
       <c r="G49" s="1" t="n">
-        <v>45901.55208333334</v>
+        <v>45902.38541666666</v>
       </c>
       <c r="H49" t="n">
-        <v>141.39</v>
+        <v>144.9</v>
       </c>
       <c r="I49" t="n">
         <v>144.8990097185983</v>
       </c>
       <c r="J49" s="2" t="n">
-        <v>48</v>
+        <v>48.83333333333334</v>
       </c>
       <c r="K49" t="n">
-        <v>13.07</v>
+        <v>10.91</v>
       </c>
       <c r="L49" t="n">
         <v>5</v>
@@ -3243,7 +3830,19 @@
         <v>1</v>
       </c>
       <c r="Q49" t="n">
-        <v>65</v>
+        <v>66</v>
+      </c>
+      <c r="R49" s="3" t="n">
+        <v>45869</v>
+      </c>
+      <c r="S49" t="b">
+        <v>1</v>
+      </c>
+      <c r="T49" t="n">
+        <v>3</v>
+      </c>
+      <c r="U49" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="50">
@@ -3270,19 +3869,19 @@
         <v>7.08</v>
       </c>
       <c r="G50" s="1" t="n">
-        <v>45924.38541666666</v>
+        <v>45924.55208333334</v>
       </c>
       <c r="H50" t="n">
-        <v>146.38</v>
+        <v>144.48</v>
       </c>
       <c r="I50" t="n">
         <v>145.7099840905977</v>
       </c>
       <c r="J50" s="2" t="n">
-        <v>22</v>
+        <v>22.16666666666667</v>
       </c>
       <c r="K50" t="n">
-        <v>1.02</v>
+        <v>-0.29</v>
       </c>
       <c r="L50" t="n">
         <v>2.66</v>
@@ -3300,7 +3899,19 @@
         <v>0</v>
       </c>
       <c r="Q50" t="n">
-        <v>33</v>
+        <v>34</v>
+      </c>
+      <c r="R50" s="3" t="n">
+        <v>45930</v>
+      </c>
+      <c r="S50" t="b">
+        <v>0</v>
+      </c>
+      <c r="T50" t="n">
+        <v>1</v>
+      </c>
+      <c r="U50" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="51">
@@ -3327,19 +3938,19 @@
         <v>6.31</v>
       </c>
       <c r="G51" s="1" t="n">
-        <v>45939.38541666666</v>
+        <v>45939.55208333334</v>
       </c>
       <c r="H51" t="n">
-        <v>145.83</v>
+        <v>147.26</v>
       </c>
       <c r="I51" t="n">
         <v>146.2702281512014</v>
       </c>
       <c r="J51" s="2" t="n">
-        <v>14.83333333333333</v>
+        <v>15</v>
       </c>
       <c r="K51" t="n">
-        <v>-0.93</v>
+        <v>-1.92</v>
       </c>
       <c r="L51" t="n">
         <v>2.3</v>
@@ -3357,7 +3968,19 @@
         <v>0</v>
       </c>
       <c r="Q51" t="n">
-        <v>20</v>
+        <v>21</v>
+      </c>
+      <c r="R51" s="3" t="n">
+        <v>45930</v>
+      </c>
+      <c r="S51" t="b">
+        <v>1</v>
+      </c>
+      <c r="T51" t="n">
+        <v>2</v>
+      </c>
+      <c r="U51" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="52">
@@ -3384,19 +4007,19 @@
         <v>6.52</v>
       </c>
       <c r="G52" s="1" t="n">
-        <v>45968.55208333334</v>
+        <v>45971.38541666666</v>
       </c>
       <c r="H52" t="n">
-        <v>149.15</v>
+        <v>148.83</v>
       </c>
       <c r="I52" t="n">
         <v>149.081146252152</v>
       </c>
       <c r="J52" s="2" t="n">
-        <v>29</v>
+        <v>31.83333333333333</v>
       </c>
       <c r="K52" t="n">
-        <v>1.28</v>
+        <v>1.07</v>
       </c>
       <c r="L52" t="n">
         <v>1.92</v>
@@ -3414,7 +4037,19 @@
         <v>1</v>
       </c>
       <c r="Q52" t="n">
-        <v>38</v>
+        <v>39</v>
+      </c>
+      <c r="R52" s="3" t="n">
+        <v>45958</v>
+      </c>
+      <c r="S52" t="b">
+        <v>1</v>
+      </c>
+      <c r="T52" t="n">
+        <v>2</v>
+      </c>
+      <c r="U52" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="53">
@@ -3441,19 +4076,19 @@
         <v>6.33</v>
       </c>
       <c r="G53" s="1" t="n">
-        <v>46059.55208333334</v>
+        <v>46062.38541666666</v>
       </c>
       <c r="H53" t="n">
-        <v>106.2</v>
+        <v>111.68</v>
       </c>
       <c r="I53" t="n">
         <v>111.6428105067877</v>
       </c>
       <c r="J53" s="2" t="n">
-        <v>88.16666666666667</v>
+        <v>91</v>
       </c>
       <c r="K53" t="n">
-        <v>28.64</v>
+        <v>24.96</v>
       </c>
       <c r="L53" t="n">
         <v>3.24</v>
@@ -3462,7 +4097,7 @@
         <v>3.99</v>
       </c>
       <c r="N53" t="n">
-        <v>4.24</v>
+        <v>4.99</v>
       </c>
       <c r="O53" t="n">
         <v>2.32</v>
@@ -3471,7 +4106,19 @@
         <v>0</v>
       </c>
       <c r="Q53" t="n">
-        <v>126</v>
+        <v>127</v>
+      </c>
+      <c r="R53" s="3" t="n">
+        <v>45986</v>
+      </c>
+      <c r="S53" t="b">
+        <v>1</v>
+      </c>
+      <c r="T53" t="n">
+        <v>4</v>
+      </c>
+      <c r="U53" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="54">
@@ -3498,19 +4145,19 @@
         <v>11.18</v>
       </c>
       <c r="G54" s="1" t="n">
-        <v>46069.38541666666</v>
+        <v>46069.55208333334</v>
       </c>
       <c r="H54" t="n">
-        <v>104.66</v>
+        <v>100.74</v>
       </c>
       <c r="I54" t="n">
         <v>102.7209264713311</v>
       </c>
       <c r="J54" s="2" t="n">
-        <v>7</v>
+        <v>7.166666666666667</v>
       </c>
       <c r="K54" t="n">
-        <v>-6.29</v>
+        <v>-9.800000000000001</v>
       </c>
       <c r="L54" t="n">
         <v>12.67</v>
@@ -3528,7 +4175,19 @@
         <v>1</v>
       </c>
       <c r="Q54" t="n">
-        <v>11</v>
+        <v>12</v>
+      </c>
+      <c r="R54" s="3" t="n">
+        <v>46077</v>
+      </c>
+      <c r="S54" t="b">
+        <v>0</v>
+      </c>
+      <c r="T54" t="n">
+        <v>1</v>
+      </c>
+      <c r="U54" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="55">
@@ -3555,28 +4214,28 @@
         <v>12.7</v>
       </c>
       <c r="G55" s="1" t="n">
-        <v>46119.55208333334</v>
+        <v>46120.38541666666</v>
       </c>
       <c r="H55" t="n">
-        <v>80.84999999999999</v>
+        <v>86.95</v>
       </c>
       <c r="I55" t="n">
         <v>84.35586720868346</v>
       </c>
       <c r="J55" s="2" t="n">
-        <v>50</v>
+        <v>50.83333333333334</v>
       </c>
       <c r="K55" t="n">
-        <v>19.74</v>
+        <v>13.69</v>
       </c>
       <c r="L55" t="n">
         <v>4.92</v>
       </c>
       <c r="M55" t="n">
-        <v>4.04</v>
+        <v>5.13</v>
       </c>
       <c r="N55" t="n">
-        <v>7.34</v>
+        <v>7.43</v>
       </c>
       <c r="O55" t="n">
         <v>-5.05</v>
@@ -3585,7 +4244,19 @@
         <v>1</v>
       </c>
       <c r="Q55" t="n">
-        <v>65</v>
+        <v>66</v>
+      </c>
+      <c r="R55" s="3" t="n">
+        <v>46077</v>
+      </c>
+      <c r="S55" t="b">
+        <v>1</v>
+      </c>
+      <c r="T55" t="n">
+        <v>3</v>
+      </c>
+      <c r="U55" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="56">
@@ -3612,19 +4283,19 @@
         <v>11.7</v>
       </c>
       <c r="G56" s="1" t="n">
-        <v>46153.55208333334</v>
+        <v>46154.38541666666</v>
       </c>
       <c r="H56" t="n">
-        <v>100.1</v>
+        <v>97.45</v>
       </c>
       <c r="I56" t="n">
         <v>98.65717542631832</v>
       </c>
       <c r="J56" s="2" t="n">
-        <v>33.16666666666666</v>
+        <v>34</v>
       </c>
       <c r="K56" t="n">
-        <v>15.12</v>
+        <v>12.08</v>
       </c>
       <c r="L56" t="n">
         <v>4.83</v>
@@ -3633,7 +4304,7 @@
         <v>2.36</v>
       </c>
       <c r="N56" t="n">
-        <v>3.42</v>
+        <v>4.3</v>
       </c>
       <c r="O56" t="n">
         <v>7.43</v>
@@ -3642,7 +4313,19 @@
         <v>1</v>
       </c>
       <c r="Q56" t="n">
-        <v>44</v>
+        <v>45</v>
+      </c>
+      <c r="R56" s="3" t="n">
+        <v>46140</v>
+      </c>
+      <c r="S56" t="b">
+        <v>1</v>
+      </c>
+      <c r="T56" t="n">
+        <v>2</v>
+      </c>
+      <c r="U56" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="57">
@@ -3669,25 +4352,25 @@
         <v>9.93</v>
       </c>
       <c r="G57" s="1" t="n">
-        <v>46185.55208333334</v>
+        <v>46188.38541666666</v>
       </c>
       <c r="H57" t="n">
-        <v>88.02</v>
+        <v>91</v>
       </c>
       <c r="I57" t="n">
         <v>88.21650097807303</v>
       </c>
       <c r="J57" s="2" t="n">
-        <v>31.16666666666667</v>
+        <v>34</v>
       </c>
       <c r="K57" t="n">
-        <v>9.68</v>
+        <v>6.62</v>
       </c>
       <c r="L57" t="n">
         <v>3.16</v>
       </c>
       <c r="M57" t="n">
-        <v>1.99</v>
+        <v>2.82</v>
       </c>
       <c r="N57" t="n">
         <v>8.16</v>
@@ -3699,7 +4382,19 @@
         <v>1</v>
       </c>
       <c r="Q57" t="n">
-        <v>46</v>
+        <v>47</v>
+      </c>
+      <c r="R57" s="3" t="n">
+        <v>46168</v>
+      </c>
+      <c r="S57" t="b">
+        <v>1</v>
+      </c>
+      <c r="T57" t="n">
+        <v>2</v>
+      </c>
+      <c r="U57" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="58">
@@ -3726,22 +4421,22 @@
         <v>9.140000000000001</v>
       </c>
       <c r="G58" s="1" t="n">
-        <v>46209.55208333334</v>
+        <v>46210.38541666666</v>
       </c>
       <c r="H58" t="n">
-        <v>86.90000000000001</v>
+        <v>85.90000000000001</v>
       </c>
       <c r="I58" t="n">
         <v>85.92363837094197</v>
       </c>
       <c r="J58" s="2" t="n">
-        <v>21.16666666666667</v>
+        <v>22</v>
       </c>
       <c r="K58" t="n">
-        <v>-4.51</v>
+        <v>-5.6</v>
       </c>
       <c r="L58" t="n">
-        <v>5</v>
+        <v>6.2</v>
       </c>
       <c r="M58" t="n">
         <v>0.32</v>
@@ -3756,7 +4451,19 @@
         <v>0</v>
       </c>
       <c r="Q58" t="n">
-        <v>30</v>
+        <v>31</v>
+      </c>
+      <c r="R58" s="3" t="n">
+        <v>46203</v>
+      </c>
+      <c r="S58" t="b">
+        <v>1</v>
+      </c>
+      <c r="T58" t="n">
+        <v>2</v>
+      </c>
+      <c r="U58" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="59">
@@ -3783,19 +4490,19 @@
         <v>5.81</v>
       </c>
       <c r="G59" s="1" t="n">
-        <v>46251.38541666666</v>
+        <v>46251.55208333334</v>
       </c>
       <c r="H59" t="n">
-        <v>77.05</v>
+        <v>78.2</v>
       </c>
       <c r="I59" t="n">
         <v>77.52467321447146</v>
       </c>
       <c r="J59" s="2" t="n">
-        <v>41</v>
+        <v>41.16666666666666</v>
       </c>
       <c r="K59" t="n">
-        <v>10.3</v>
+        <v>8.960000000000001</v>
       </c>
       <c r="L59" t="n">
         <v>1.33</v>
@@ -3813,7 +4520,19 @@
         <v>0</v>
       </c>
       <c r="Q59" t="n">
-        <v>59</v>
+        <v>60</v>
+      </c>
+      <c r="R59" s="3" t="n">
+        <v>46231</v>
+      </c>
+      <c r="S59" t="b">
+        <v>1</v>
+      </c>
+      <c r="T59" t="n">
+        <v>2</v>
+      </c>
+      <c r="U59" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="60">
@@ -3840,22 +4559,22 @@
         <v>6.78</v>
       </c>
       <c r="G60" s="1" t="n">
-        <v>46260.55208333334</v>
+        <v>46261.38541666666</v>
       </c>
       <c r="H60" t="n">
-        <v>73.2</v>
+        <v>71.78</v>
       </c>
       <c r="I60" t="n">
         <v>72.89991469627812</v>
       </c>
       <c r="J60" s="2" t="n">
-        <v>9</v>
+        <v>9.833333333333334</v>
       </c>
       <c r="K60" t="n">
-        <v>-6.39</v>
+        <v>-8.210000000000001</v>
       </c>
       <c r="L60" t="n">
-        <v>6.92</v>
+        <v>8.34</v>
       </c>
       <c r="M60" t="n">
         <v>0.26</v>
@@ -3870,7 +4589,19 @@
         <v>1</v>
       </c>
       <c r="Q60" t="n">
-        <v>15</v>
+        <v>16</v>
+      </c>
+      <c r="R60" s="3" t="n">
+        <v>46259</v>
+      </c>
+      <c r="S60" t="b">
+        <v>1</v>
+      </c>
+      <c r="T60" t="n">
+        <v>2</v>
+      </c>
+      <c r="U60" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="61">
@@ -3897,22 +4628,22 @@
         <v>6.42</v>
       </c>
       <c r="G61" s="1" t="n">
-        <v>46268.38541666666</v>
+        <v>46268.55208333334</v>
       </c>
       <c r="H61" t="n">
-        <v>72</v>
+        <v>74.5</v>
       </c>
       <c r="I61" t="n">
         <v>72.90237723585678</v>
       </c>
       <c r="J61" s="2" t="n">
-        <v>7</v>
+        <v>7.166666666666667</v>
       </c>
       <c r="K61" t="n">
-        <v>-0.31</v>
+        <v>-3.79</v>
       </c>
       <c r="L61" t="n">
-        <v>2.67</v>
+        <v>3.87</v>
       </c>
       <c r="M61" t="n">
         <v>2.36</v>
@@ -3927,7 +4658,19 @@
         <v>0</v>
       </c>
       <c r="Q61" t="n">
-        <v>11</v>
+        <v>12</v>
+      </c>
+      <c r="R61" s="3" t="n">
+        <v>46294</v>
+      </c>
+      <c r="S61" t="b">
+        <v>0</v>
+      </c>
+      <c r="T61" t="n">
+        <v>1</v>
+      </c>
+      <c r="U61" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="62">
@@ -3954,19 +4697,19 @@
         <v>8.02</v>
       </c>
       <c r="G62" s="1" t="n">
-        <v>46289.38541666666</v>
+        <v>46289.55208333334</v>
       </c>
       <c r="H62" t="n">
-        <v>74.08</v>
+        <v>73.04000000000001</v>
       </c>
       <c r="I62" t="n">
         <v>73.68623612571655</v>
       </c>
       <c r="J62" s="2" t="n">
-        <v>20.83333333333333</v>
+        <v>21</v>
       </c>
       <c r="K62" t="n">
-        <v>-0.5600000000000001</v>
+        <v>-1.96</v>
       </c>
       <c r="L62" t="n">
         <v>3.68</v>
@@ -3984,7 +4727,19 @@
         <v>1</v>
       </c>
       <c r="Q62" t="n">
-        <v>28</v>
+        <v>29</v>
+      </c>
+      <c r="R62" s="3" t="n">
+        <v>46294</v>
+      </c>
+      <c r="S62" t="b">
+        <v>0</v>
+      </c>
+      <c r="T62" t="n">
+        <v>1</v>
+      </c>
+      <c r="U62" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="63">
@@ -4011,19 +4766,19 @@
         <v>6.76</v>
       </c>
       <c r="G63" s="1" t="n">
-        <v>46308.38541666666</v>
+        <v>46308.55208333334</v>
       </c>
       <c r="H63" t="n">
-        <v>68.51000000000001</v>
+        <v>69.98</v>
       </c>
       <c r="I63" t="n">
         <v>68.61676463622267</v>
       </c>
       <c r="J63" s="2" t="n">
-        <v>18.83333333333333</v>
+        <v>19</v>
       </c>
       <c r="K63" t="n">
-        <v>6.2</v>
+        <v>4.19</v>
       </c>
       <c r="L63" t="n">
         <v>3.37</v>
@@ -4041,7 +4796,19 @@
         <v>0</v>
       </c>
       <c r="Q63" t="n">
-        <v>24</v>
+        <v>25</v>
+      </c>
+      <c r="R63" s="3" t="n">
+        <v>46294</v>
+      </c>
+      <c r="S63" t="b">
+        <v>1</v>
+      </c>
+      <c r="T63" t="n">
+        <v>2</v>
+      </c>
+      <c r="U63" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="64">
@@ -4068,22 +4835,22 @@
         <v>9.41</v>
       </c>
       <c r="G64" s="1" t="n">
-        <v>46314.55208333334</v>
+        <v>46316.38541666666</v>
       </c>
       <c r="H64" t="n">
-        <v>64.97</v>
+        <v>62.66</v>
       </c>
       <c r="I64" t="n">
         <v>64.76461076631858</v>
       </c>
       <c r="J64" s="2" t="n">
-        <v>6</v>
+        <v>7.833333333333333</v>
       </c>
       <c r="K64" t="n">
-        <v>-7.16</v>
+        <v>-10.46</v>
       </c>
       <c r="L64" t="n">
-        <v>7.43</v>
+        <v>10.5</v>
       </c>
       <c r="M64" t="n">
         <v>1.01</v>
@@ -4098,7 +4865,19 @@
         <v>1</v>
       </c>
       <c r="Q64" t="n">
-        <v>9</v>
+        <v>10</v>
+      </c>
+      <c r="R64" s="3" t="n">
+        <v>46322</v>
+      </c>
+      <c r="S64" t="b">
+        <v>0</v>
+      </c>
+      <c r="T64" t="n">
+        <v>1</v>
+      </c>
+      <c r="U64" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="65">
@@ -4149,6 +4928,12 @@
       <c r="Q65" t="n">
         <v>10</v>
       </c>
+      <c r="R65" s="3" t="n">
+        <v>46322</v>
+      </c>
+      <c r="S65" t="inlineStr"/>
+      <c r="T65" t="inlineStr"/>
+      <c r="U65" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -6251,7 +7036,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>26.7</v>
+        <v>27.7</v>
       </c>
     </row>
     <row r="6">
@@ -6261,7 +7046,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="7">
@@ -6271,7 +7056,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>112</v>
+        <v>112.2</v>
       </c>
     </row>
     <row r="8">
@@ -6281,7 +7066,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>3</v>
+        <v>3.8</v>
       </c>
     </row>
     <row r="9">
@@ -6291,7 +7076,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>34.7</v>
+        <v>35.5</v>
       </c>
     </row>
     <row r="10">
@@ -6301,7 +7086,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>56.6</v>
+        <v>56.7</v>
       </c>
     </row>
     <row r="11">
@@ -6311,7 +7096,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>44</v>
+        <v>43</v>
       </c>
     </row>
     <row r="12">
@@ -6321,7 +7106,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="13">
@@ -6331,7 +7116,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>69.8</v>
+        <v>68.3</v>
       </c>
     </row>
     <row r="14">
@@ -6341,7 +7126,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>6.67</v>
+        <v>2.33</v>
       </c>
     </row>
     <row r="15">
@@ -6351,7 +7136,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>9.32</v>
+        <v>5</v>
       </c>
     </row>
     <row r="16">
@@ -6361,7 +7146,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>3.93</v>
+        <v>-0.41</v>
       </c>
     </row>
     <row r="17">
@@ -6371,7 +7156,7 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>111.51</v>
+        <v>94.34</v>
       </c>
     </row>
     <row r="18">
@@ -6381,7 +7166,7 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>55.6</v>
+        <v>39.7</v>
       </c>
     </row>
     <row r="19">
@@ -6391,7 +7176,7 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>6.23</v>
+        <v>7.37</v>
       </c>
     </row>
     <row r="20">
@@ -6401,7 +7186,7 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>5.35</v>
+        <v>6.43</v>
       </c>
     </row>
     <row r="21">
@@ -6411,7 +7196,7 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>17.64</v>
+        <v>21.79</v>
       </c>
     </row>
     <row r="22">
@@ -6421,7 +7206,7 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>33</v>
+        <v>39</v>
       </c>
     </row>
     <row r="23">
@@ -6431,7 +7216,7 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>11</v>
+        <v>18</v>
       </c>
     </row>
     <row r="24">
@@ -6441,7 +7226,7 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>2.1</v>
+        <v>2.41</v>
       </c>
     </row>
     <row r="25">
@@ -6451,7 +7236,7 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>6.8</v>
+        <v>7.37</v>
       </c>
     </row>
     <row r="26">
@@ -6461,7 +7246,7 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>5.24</v>
+        <v>6.2</v>
       </c>
     </row>
     <row r="27">
@@ -6471,7 +7256,7 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>10.25</v>
+        <v>20.03</v>
       </c>
     </row>
     <row r="28">
@@ -6481,7 +7266,7 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>46</v>
+        <v>52</v>
       </c>
     </row>
     <row r="29">
